--- a/exports/INFY_full_report.xlsx
+++ b/exports/INFY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>6.01</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1825.5</v>
+        <v>1788</v>
       </c>
       <c r="I2" t="n">
         <v>1821.676822029427</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.11</v>
+        <v>-2.16</v>
       </c>
       <c r="L2" t="n">
         <v>2.88</v>
       </c>
       <c r="M2" t="n">
-        <v>0.87</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
         <v>2.72</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>4.94</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1735.5</v>
+        <v>1751</v>
       </c>
       <c r="I3" t="n">
         <v>1736.914761320004</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>2.94</v>
+        <v>2.07</v>
       </c>
       <c r="L3" t="n">
         <v>1.17</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>5.92</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>1670.8</v>
+        <v>1648.3</v>
       </c>
       <c r="I4" t="n">
         <v>1658.960532381262</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.58</v>
+        <v>-5.87</v>
       </c>
       <c r="L4" t="n">
-        <v>6.03</v>
+        <v>6.19</v>
       </c>
       <c r="M4" t="n">
         <v>1.79</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>5.9</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44627.55208333334</v>
+        <v>44628.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1703.9</v>
+        <v>1747.2</v>
       </c>
       <c r="I5" t="n">
         <v>1741.746120831938</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.37</v>
+        <v>-6</v>
       </c>
       <c r="L5" t="n">
-        <v>4.4</v>
+        <v>6.23</v>
       </c>
       <c r="M5" t="n">
         <v>2.39</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.67</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44657.55208333334</v>
+        <v>44658.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1790.3</v>
+        <v>1786.1</v>
       </c>
       <c r="I6" t="n">
         <v>1789.510572997755</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="L6" t="n">
         <v>3.73</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>3.5</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1435.4</v>
+        <v>1494.6</v>
       </c>
       <c r="I7" t="n">
         <v>1460.562939288365</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K7" t="n">
-        <v>19.63</v>
+        <v>16.32</v>
       </c>
       <c r="L7" t="n">
         <v>0.73</v>
@@ -840,7 +923,7 @@
         <v>1.58</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>4.32</v>
       </c>
       <c r="O7" t="n">
         <v>-0.71</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.14</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1443.8</v>
+        <v>1394.4</v>
       </c>
       <c r="I8" t="n">
         <v>1423.983005444994</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.4</v>
+        <v>-6.7</v>
       </c>
       <c r="L8" t="n">
-        <v>3.58</v>
+        <v>6.9</v>
       </c>
       <c r="M8" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
         <v>4.32</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>6.08</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1410.8</v>
+        <v>1446</v>
       </c>
       <c r="I9" t="n">
         <v>1426.975999395539</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.18</v>
+        <v>-3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>2.98</v>
+        <v>4.02</v>
       </c>
       <c r="M9" t="n">
-        <v>1.17</v>
+        <v>1.86</v>
       </c>
       <c r="N9" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
         <v>-3.25</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.35</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44753.55208333334</v>
+        <v>44754.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1439.5</v>
+        <v>1414.2</v>
       </c>
       <c r="I10" t="n">
         <v>1417.07052214484</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.45</v>
+        <v>-2.2</v>
       </c>
       <c r="L10" t="n">
         <v>2.37</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>5.4</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44757.55208333334</v>
+        <v>44760.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1404.5</v>
+        <v>1455.8</v>
       </c>
       <c r="I11" t="n">
         <v>1455.287751949568</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.94</v>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>3.21</v>
       </c>
       <c r="M11" t="n">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.76</v>
+        <v>3.91</v>
       </c>
       <c r="O11" t="n">
         <v>-2.29</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.3</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44767.55208333334</v>
+        <v>44768.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1470.2</v>
+        <v>1426.5</v>
       </c>
       <c r="I12" t="n">
         <v>1427.495450017854</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.99</v>
+        <v>-2.01</v>
       </c>
       <c r="L12" t="n">
         <v>2.53</v>
@@ -1125,7 +1268,7 @@
         <v>1.82</v>
       </c>
       <c r="N12" t="n">
-        <v>1.59</v>
+        <v>3.41</v>
       </c>
       <c r="O12" t="n">
         <v>3.91</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.79</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44770.55208333334</v>
+        <v>44771.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1485.1</v>
+        <v>1516.1</v>
       </c>
       <c r="I13" t="n">
         <v>1500.248748997062</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.11</v>
+        <v>-6.28</v>
       </c>
       <c r="L13" t="n">
-        <v>4.61</v>
+        <v>6.74</v>
       </c>
       <c r="M13" t="n">
         <v>1.9</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>5.74</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44795.55208333334</v>
+        <v>44796.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1543.6</v>
+        <v>1512.3</v>
       </c>
       <c r="I14" t="n">
         <v>1524.61328914301</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K14" t="n">
-        <v>1.81</v>
+        <v>-0.25</v>
       </c>
       <c r="L14" t="n">
         <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>0.84</v>
+        <v>1.84</v>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
         <v>1.89</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>3.96</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44813.55208333334</v>
+        <v>44816.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1479.7</v>
+        <v>1506.4</v>
       </c>
       <c r="I15" t="n">
         <v>1481.806150070622</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>2.16</v>
+        <v>0.39</v>
       </c>
       <c r="L15" t="n">
         <v>0.61</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>4.56</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44817.55208333334</v>
+        <v>44818.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1513.2</v>
+        <v>1448.7</v>
       </c>
       <c r="I16" t="n">
         <v>1459.009464517932</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.45</v>
+        <v>-3.83</v>
       </c>
       <c r="L16" t="n">
-        <v>1.16</v>
+        <v>4.22</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O16" t="n">
         <v>1.5</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.37</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1397.8</v>
+        <v>1424.9</v>
       </c>
       <c r="I17" t="n">
         <v>1406.637784707855</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>3.51</v>
+        <v>1.64</v>
       </c>
       <c r="L17" t="n">
         <v>1.24</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.95</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44868.55208333334</v>
+        <v>44869.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1497.6</v>
+        <v>1471.7</v>
       </c>
       <c r="I18" t="n">
         <v>1480.865098336885</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>3.28</v>
       </c>
       <c r="L18" t="n">
         <v>2.86</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>4.28</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44875.55208333334</v>
+        <v>44876.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1471.2</v>
+        <v>1529.8</v>
       </c>
       <c r="I19" t="n">
         <v>1524.833420189221</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.03</v>
+        <v>-3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.69</v>
+        <v>4.51</v>
       </c>
       <c r="M19" t="n">
-        <v>1.46</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.17</v>
+        <v>4.52</v>
       </c>
       <c r="O19" t="n">
         <v>-0.85</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.89</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1585.7</v>
+        <v>1540.2</v>
       </c>
       <c r="I20" t="n">
         <v>1565.944714968874</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>3.65</v>
+        <v>0.68</v>
       </c>
       <c r="L20" t="n">
         <v>1.04</v>
@@ -1581,7 +1820,7 @@
         <v>0.83</v>
       </c>
       <c r="N20" t="n">
-        <v>1.52</v>
+        <v>3.21</v>
       </c>
       <c r="O20" t="n">
         <v>4.52</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.82</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44938.55208333334</v>
+        <v>44939.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1451.9</v>
+        <v>1481.7</v>
       </c>
       <c r="I21" t="n">
         <v>1470.482996616859</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K21" t="n">
-        <v>5.73</v>
+        <v>3.8</v>
       </c>
       <c r="L21" t="n">
         <v>3.46</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.98</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44980.38541666666</v>
+        <v>44980.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>1526.9</v>
+        <v>1518.8</v>
       </c>
       <c r="I22" t="n">
         <v>1519.454924811121</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="L22" t="n">
         <v>3.02</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>3.4</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45016.38541666666</v>
+        <v>45016.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>1388.4</v>
+        <v>1395.5</v>
       </c>
       <c r="I23" t="n">
         <v>1394.007673050561</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K23" t="n">
-        <v>8.59</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>1.11</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>3.93</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1355.6</v>
+        <v>1214</v>
       </c>
       <c r="I24" t="n">
         <v>1348.441691403596</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.86</v>
+        <v>-13.01</v>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>14.48</v>
       </c>
       <c r="M24" t="n">
-        <v>1.37</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>9.06</v>
       </c>
       <c r="O24" t="n">
         <v>2.66</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>7.9</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1226.4</v>
+        <v>1250.3</v>
       </c>
       <c r="I25" t="n">
         <v>1247.744767163197</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.02</v>
+        <v>-2.99</v>
       </c>
       <c r="L25" t="n">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="M25" t="n">
         <v>0.84</v>
       </c>
       <c r="N25" t="n">
-        <v>1.52</v>
+        <v>2.01</v>
       </c>
       <c r="O25" t="n">
         <v>-9.06</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>4.47</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45082.55208333334</v>
+        <v>45083.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1278.3</v>
+        <v>1250.6</v>
       </c>
       <c r="I26" t="n">
         <v>1259.373296534952</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K26" t="n">
-        <v>2.24</v>
+        <v>0.02</v>
       </c>
       <c r="L26" t="n">
         <v>2.98</v>
       </c>
       <c r="M26" t="n">
-        <v>0.95</v>
+        <v>1.33</v>
       </c>
       <c r="N26" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="O26" t="n">
         <v>2.01</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>3.52</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45089.55208333334</v>
+        <v>45090.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1265.3</v>
+        <v>1278.3</v>
       </c>
       <c r="I27" t="n">
         <v>1272.548764844419</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.18</v>
+        <v>-2.21</v>
       </c>
       <c r="L27" t="n">
-        <v>1.42</v>
+        <v>2.24</v>
       </c>
       <c r="M27" t="n">
         <v>0.74</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>3.14</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>1248</v>
+        <v>1238.2</v>
       </c>
       <c r="I28" t="n">
         <v>1242.253815748192</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.37</v>
+        <v>-3.14</v>
       </c>
       <c r="L28" t="n">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="M28" t="n">
         <v>0.7</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>3.2</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1269.2</v>
+        <v>1303.3</v>
       </c>
       <c r="I29" t="n">
         <v>1276.078306504965</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.5</v>
+        <v>-5.26</v>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>5.32</v>
       </c>
       <c r="M29" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="N29" t="n">
-        <v>1.38</v>
+        <v>3.18</v>
       </c>
       <c r="O29" t="n">
         <v>-1.44</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>3.97</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45127.55208333334</v>
+        <v>45128.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1412.2</v>
+        <v>1304</v>
       </c>
       <c r="I30" t="n">
         <v>1374.959966096553</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
-        <v>8.359999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="L30" t="n">
         <v>2.03</v>
       </c>
       <c r="M30" t="n">
-        <v>0.66</v>
+        <v>8.5</v>
       </c>
       <c r="N30" t="n">
-        <v>2.32</v>
+        <v>7.3</v>
       </c>
       <c r="O30" t="n">
         <v>3.18</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>7.66</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45152.55208333334</v>
+        <v>45154.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1363.4</v>
+        <v>1388.4</v>
       </c>
       <c r="I31" t="n">
         <v>1370.929988165571</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.56</v>
+        <v>-6.47</v>
       </c>
       <c r="L31" t="n">
-        <v>4.85</v>
+        <v>6.55</v>
       </c>
       <c r="M31" t="n">
-        <v>0.73</v>
+        <v>1.28</v>
       </c>
       <c r="N31" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="O31" t="n">
         <v>-7.3</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>3.59</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45194.38541666666</v>
+        <v>45194.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1450.4</v>
+        <v>1444.2</v>
       </c>
       <c r="I32" t="n">
         <v>1445.172579104342</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>4.47</v>
+        <v>4.02</v>
       </c>
       <c r="L32" t="n">
         <v>2.28</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>3.09</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45204.55208333334</v>
+        <v>45205.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1430.2</v>
+        <v>1449</v>
       </c>
       <c r="I33" t="n">
         <v>1441.012748525111</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>0.97</v>
+        <v>-0.33</v>
       </c>
       <c r="L33" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="M33" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="N33" t="n">
         <v>1.39</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>4.03</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45211.55208333334</v>
+        <v>45212.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1421.5</v>
+        <v>1395.4</v>
       </c>
       <c r="I34" t="n">
         <v>1411.649806508271</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.9</v>
+        <v>-3.7</v>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>5.43</v>
       </c>
       <c r="M34" t="n">
-        <v>0.97</v>
+        <v>3.26</v>
       </c>
       <c r="N34" t="n">
         <v>2.57</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>4.57</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45245.38541666666</v>
+        <v>45245.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1371.3</v>
+        <v>1382.1</v>
       </c>
       <c r="I35" t="n">
         <v>1374.806833630168</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>1.73</v>
+        <v>0.95</v>
       </c>
       <c r="L35" t="n">
         <v>1.99</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>3.49</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45272.55208333334</v>
+        <v>45273.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1445.7</v>
+        <v>1409.5</v>
       </c>
       <c r="I36" t="n">
         <v>1415.890282464335</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>4.6</v>
+        <v>1.98</v>
       </c>
       <c r="L36" t="n">
         <v>0.8100000000000001</v>
@@ -2493,7 +2924,7 @@
         <v>0.8</v>
       </c>
       <c r="N36" t="n">
-        <v>0.88</v>
+        <v>1.83</v>
       </c>
       <c r="O36" t="n">
         <v>2.78</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>4.62</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45274.38541666666</v>
+        <v>45274.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1458.8</v>
+        <v>1474.1</v>
       </c>
       <c r="I37" t="n">
         <v>1463.85984567515</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.5</v>
+        <v>-4.58</v>
       </c>
       <c r="L37" t="n">
-        <v>4.03</v>
+        <v>4.93</v>
       </c>
       <c r="M37" t="n">
         <v>0.93</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>4.39</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45294.38541666666</v>
+        <v>45294.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>1469.2</v>
+        <v>1460.3</v>
       </c>
       <c r="I38" t="n">
         <v>1468.129296227281</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.33</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="M38" t="n">
         <v>1.62</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>4.16</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45302.55208333334</v>
+        <v>45303.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1488.1</v>
+        <v>1573</v>
       </c>
       <c r="I39" t="n">
         <v>1521.062030178485</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.9</v>
+        <v>-7.72</v>
       </c>
       <c r="L39" t="n">
-        <v>4.1</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>1.51</v>
+        <v>2.74</v>
       </c>
       <c r="N39" t="n">
-        <v>1.42</v>
+        <v>6.23</v>
       </c>
       <c r="O39" t="n">
         <v>-2.71</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>7.02</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45335.55208333334</v>
+        <v>45336.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1644.8</v>
+        <v>1613.1</v>
       </c>
       <c r="I40" t="n">
         <v>1619.475688082117</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K40" t="n">
-        <v>4.56</v>
+        <v>2.55</v>
       </c>
       <c r="L40" t="n">
         <v>3.21</v>
       </c>
       <c r="M40" t="n">
-        <v>0.49</v>
+        <v>1.2</v>
       </c>
       <c r="N40" t="n">
         <v>1.97</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>4.52</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45433.55208333334</v>
+        <v>45434.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1405.1</v>
+        <v>1427.4</v>
       </c>
       <c r="I41" t="n">
         <v>1424.068436265744</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>97.16666666666667</v>
+        <v>98</v>
       </c>
       <c r="K41" t="n">
-        <v>12.89</v>
+        <v>11.51</v>
       </c>
       <c r="L41" t="n">
         <v>3.85</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.25</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45442.55208333334</v>
+        <v>45443.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1404.5</v>
+        <v>1397.3</v>
       </c>
       <c r="I42" t="n">
         <v>1399.037866238775</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.6</v>
+        <v>-2.11</v>
       </c>
       <c r="L42" t="n">
-        <v>2.52</v>
+        <v>3.97</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7</v>
+        <v>1.75</v>
       </c>
       <c r="N42" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="O42" t="n">
         <v>1.31</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>2.66</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45448.55208333334</v>
+        <v>45449.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1399.7</v>
+        <v>1433.2</v>
       </c>
       <c r="I43" t="n">
         <v>1422.561528736388</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.17</v>
+        <v>-2.57</v>
       </c>
       <c r="L43" t="n">
-        <v>0.87</v>
+        <v>3.04</v>
       </c>
       <c r="M43" t="n">
         <v>2.35</v>
       </c>
       <c r="N43" t="n">
-        <v>2.02</v>
+        <v>3.01</v>
       </c>
       <c r="O43" t="n">
         <v>-1.94</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>5.6</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1780.5</v>
+        <v>1700.4</v>
       </c>
       <c r="I44" t="n">
         <v>1765.052458910132</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K44" t="n">
-        <v>24.23</v>
+        <v>18.64</v>
       </c>
       <c r="L44" t="n">
         <v>1.82</v>
       </c>
       <c r="M44" t="n">
-        <v>0.85</v>
+        <v>1.88</v>
       </c>
       <c r="N44" t="n">
-        <v>2.13</v>
+        <v>3.63</v>
       </c>
       <c r="O44" t="n">
         <v>3.01</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>6.41</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45518.55208333334</v>
+        <v>45520.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1781.5</v>
+        <v>1812.8</v>
       </c>
       <c r="I45" t="n">
         <v>1796.370331581736</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.77</v>
+        <v>-6.61</v>
       </c>
       <c r="L45" t="n">
-        <v>5.05</v>
+        <v>6.78</v>
       </c>
       <c r="M45" t="n">
         <v>2.28</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>4.73</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45552.55208333334</v>
+        <v>45553.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1908.7</v>
+        <v>1853.4</v>
       </c>
       <c r="I46" t="n">
         <v>1858.391745162305</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K46" t="n">
-        <v>5.29</v>
+        <v>2.24</v>
       </c>
       <c r="L46" t="n">
         <v>1.22</v>
@@ -3063,7 +3614,7 @@
         <v>1.02</v>
       </c>
       <c r="N46" t="n">
-        <v>1.5</v>
+        <v>2.95</v>
       </c>
       <c r="O46" t="n">
         <v>2.03</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>5.01</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1904.7</v>
+        <v>1921</v>
       </c>
       <c r="I47" t="n">
         <v>1918.267111923377</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.77</v>
+        <v>-3.65</v>
       </c>
       <c r="L47" t="n">
-        <v>4.28</v>
+        <v>4.41</v>
       </c>
       <c r="M47" t="n">
         <v>2.01</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>4.51</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45582.55208333334</v>
+        <v>45583.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1933.2</v>
+        <v>1838.2</v>
       </c>
       <c r="I48" t="n">
         <v>1846.837438359764</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K48" t="n">
-        <v>0.64</v>
+        <v>-4.31</v>
       </c>
       <c r="L48" t="n">
-        <v>2.68</v>
+        <v>4.75</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4</v>
+        <v>4.11</v>
       </c>
       <c r="N48" t="n">
-        <v>2.29</v>
+        <v>4.56</v>
       </c>
       <c r="O48" t="n">
         <v>0.67</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>7.32</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1715.9</v>
+        <v>1780.3</v>
       </c>
       <c r="I49" t="n">
         <v>1777.183937280766</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K49" t="n">
-        <v>6.65</v>
+        <v>3.15</v>
       </c>
       <c r="L49" t="n">
         <v>3.13</v>
       </c>
       <c r="M49" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="N49" t="n">
-        <v>1.06</v>
+        <v>4.14</v>
       </c>
       <c r="O49" t="n">
         <v>-4.56</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.2</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1907.2</v>
+        <v>1876.4</v>
       </c>
       <c r="I50" t="n">
         <v>1878.889939674114</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K50" t="n">
-        <v>7.13</v>
+        <v>5.4</v>
       </c>
       <c r="L50" t="n">
         <v>3.09</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1845.1</v>
+        <v>1915.7</v>
       </c>
       <c r="I51" t="n">
         <v>1914.759296065235</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K51" t="n">
-        <v>1.67</v>
+        <v>-2.09</v>
       </c>
       <c r="L51" t="n">
         <v>3.28</v>
@@ -3348,7 +3959,7 @@
         <v>1.37</v>
       </c>
       <c r="N51" t="n">
-        <v>0.42</v>
+        <v>3.7</v>
       </c>
       <c r="O51" t="n">
         <v>-1.06</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>6.39</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45673.55208333334</v>
+        <v>45674.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1879.4</v>
+        <v>1779.2</v>
       </c>
       <c r="I52" t="n">
         <v>1841.497868371486</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.89</v>
+        <v>-7.13</v>
       </c>
       <c r="L52" t="n">
-        <v>3.67</v>
+        <v>7.42</v>
       </c>
       <c r="M52" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="N52" t="n">
-        <v>1.62</v>
+        <v>5.37</v>
       </c>
       <c r="O52" t="n">
         <v>3.7</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>6.66</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45692.55208333334</v>
+        <v>45693.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1854.7</v>
+        <v>1865.6</v>
       </c>
       <c r="I53" t="n">
         <v>1862.974469469968</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.24</v>
+        <v>-4.86</v>
       </c>
       <c r="L53" t="n">
-        <v>5.14</v>
+        <v>5.61</v>
       </c>
       <c r="M53" t="n">
         <v>1.34</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>4.34</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45706.55208333334</v>
+        <v>45707.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1808.9</v>
+        <v>1785.4</v>
       </c>
       <c r="I54" t="n">
         <v>1792.223169410673</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.04</v>
+        <v>-4.3</v>
       </c>
       <c r="L54" t="n">
-        <v>4.4</v>
+        <v>4.51</v>
       </c>
       <c r="M54" t="n">
         <v>0.78</v>
       </c>
       <c r="N54" t="n">
-        <v>1.29</v>
+        <v>2.04</v>
       </c>
       <c r="O54" t="n">
         <v>0.23</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.41</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1397.5</v>
+        <v>1437.3</v>
       </c>
       <c r="I55" t="n">
         <v>1435.60239450924</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K55" t="n">
-        <v>21.73</v>
+        <v>19.5</v>
       </c>
       <c r="L55" t="n">
         <v>1.38</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45849.55208333334</v>
+        <v>45852.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1560.7</v>
+        <v>1528.8</v>
       </c>
       <c r="I56" t="n">
         <v>1553.263838061008</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>81.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K56" t="n">
-        <v>8.59</v>
+        <v>6.37</v>
       </c>
       <c r="L56" t="n">
         <v>3.98</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.99</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1411.9</v>
+        <v>1456</v>
       </c>
       <c r="I57" t="n">
         <v>1446.364277567439</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K57" t="n">
-        <v>7.65</v>
+        <v>4.76</v>
       </c>
       <c r="L57" t="n">
         <v>3.21</v>
@@ -3690,7 +4373,7 @@
         <v>1.37</v>
       </c>
       <c r="N57" t="n">
-        <v>1.51</v>
+        <v>3.74</v>
       </c>
       <c r="O57" t="n">
         <v>-1.51</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.67</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45898.38541666666</v>
+        <v>45898.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>1448.8</v>
+        <v>1437.9</v>
       </c>
       <c r="I58" t="n">
         <v>1441.176276775456</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.49</v>
+        <v>-1.24</v>
       </c>
       <c r="L58" t="n">
         <v>3.15</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>4.33</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45908.55208333334</v>
+        <v>45909.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1405.5</v>
+        <v>1467.7</v>
       </c>
       <c r="I59" t="n">
         <v>1456.191808883423</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>2.25</v>
+        <v>-2.07</v>
       </c>
       <c r="L59" t="n">
         <v>2.98</v>
       </c>
       <c r="M59" t="n">
-        <v>0.59</v>
+        <v>3.14</v>
       </c>
       <c r="N59" t="n">
-        <v>2.15</v>
+        <v>4.63</v>
       </c>
       <c r="O59" t="n">
         <v>-2.06</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.46</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1468.8</v>
+        <v>1458</v>
       </c>
       <c r="I60" t="n">
         <v>1462.67325943896</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K60" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.66</v>
       </c>
       <c r="L60" t="n">
         <v>1.8</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>4.15</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45938.55208333334</v>
+        <v>45939.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1460.4</v>
+        <v>1472.9</v>
       </c>
       <c r="I61" t="n">
         <v>1461.800435339792</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.16</v>
+        <v>-1.02</v>
       </c>
       <c r="L61" t="n">
-        <v>0.88</v>
+        <v>1.64</v>
       </c>
       <c r="M61" t="n">
-        <v>0.54</v>
+        <v>0.67</v>
       </c>
       <c r="N61" t="n">
         <v>2.33</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>4.26</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45946.55208333334</v>
+        <v>45947.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1438.9</v>
+        <v>1407.6</v>
       </c>
       <c r="I62" t="n">
         <v>1426.190617953717</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.31</v>
+        <v>-4.43</v>
       </c>
       <c r="L62" t="n">
-        <v>2.94</v>
+        <v>4.53</v>
       </c>
       <c r="M62" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="N62" t="n">
-        <v>1.3</v>
+        <v>2.04</v>
       </c>
       <c r="O62" t="n">
         <v>1.18</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>4.67</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45951.57291666666</v>
+        <v>45953.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1439.8</v>
+        <v>1509.8</v>
       </c>
       <c r="I63" t="n">
         <v>1461.736686041733</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>4.1875</v>
+        <v>6</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.29</v>
+        <v>-7.26</v>
       </c>
       <c r="L63" t="n">
-        <v>3.33</v>
+        <v>7.51</v>
       </c>
       <c r="M63" t="n">
-        <v>1.05</v>
+        <v>2.65</v>
       </c>
       <c r="N63" t="n">
-        <v>1.57</v>
+        <v>3.67</v>
       </c>
       <c r="O63" t="n">
         <v>-2.04</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5.75</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45974.55208333334</v>
+        <v>45975.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1507.4</v>
+        <v>1462</v>
       </c>
       <c r="I64" t="n">
         <v>1469.047235536485</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.16</v>
+        <v>-3.17</v>
       </c>
       <c r="L64" t="n">
         <v>6.05</v>
       </c>
       <c r="M64" t="n">
-        <v>0.91</v>
+        <v>1.3</v>
       </c>
       <c r="N64" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="O64" t="n">
         <v>3.67</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.4</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1503.8</v>
+        <v>1513.9</v>
       </c>
       <c r="I65" t="n">
         <v>1510.847630647396</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.86</v>
+        <v>-3.55</v>
       </c>
       <c r="L65" t="n">
         <v>4.11</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>4.41</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46021.38541666666</v>
+        <v>46021.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>1600.8</v>
+        <v>1588.6</v>
       </c>
       <c r="I66" t="n">
         <v>1594.41792103924</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K66" t="n">
-        <v>5.74</v>
+        <v>4.93</v>
       </c>
       <c r="L66" t="n">
         <v>1.34</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>3.74</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46036.55208333334</v>
+        <v>46038.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1573</v>
+        <v>1650.3</v>
       </c>
       <c r="I67" t="n">
         <v>1617.355837506401</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>15</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>0.98</v>
+        <v>-3.88</v>
       </c>
       <c r="L67" t="n">
-        <v>1.32</v>
+        <v>4.31</v>
       </c>
       <c r="M67" t="n">
-        <v>1.25</v>
+        <v>3.53</v>
       </c>
       <c r="N67" t="n">
-        <v>2.18</v>
+        <v>5.1</v>
       </c>
       <c r="O67" t="n">
         <v>-1.34</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>5.66</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46051.55208333334</v>
+        <v>46052.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1625.8</v>
+        <v>1593.1</v>
       </c>
       <c r="I68" t="n">
         <v>1593.588280526253</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.48</v>
+        <v>-3.47</v>
       </c>
       <c r="L68" t="n">
-        <v>3.25</v>
+        <v>4.03</v>
       </c>
       <c r="M68" t="n">
         <v>0.48</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>4.61</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46114.38541666666</v>
+        <v>46114.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>1246.6</v>
+        <v>1270.5</v>
       </c>
       <c r="I69" t="n">
         <v>1269.065866204142</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>62</v>
+        <v>62.16666666666666</v>
       </c>
       <c r="K69" t="n">
-        <v>21.75</v>
+        <v>20.25</v>
       </c>
       <c r="L69" t="n">
         <v>6.17</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>6.68</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46133.55208333334</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1286.8</v>
+        <v>1235.1</v>
       </c>
       <c r="I70" t="n">
         <v>1243.993463149661</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>1.28</v>
+        <v>-2.79</v>
       </c>
       <c r="L70" t="n">
-        <v>2.49</v>
+        <v>3.24</v>
       </c>
       <c r="M70" t="n">
         <v>1.5</v>
       </c>
       <c r="N70" t="n">
-        <v>2.94</v>
+        <v>3.49</v>
       </c>
       <c r="O70" t="n">
         <v>1.57</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>6.82</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46160.55208333334</v>
+        <v>46161.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1121.3</v>
+        <v>1164.6</v>
       </c>
       <c r="I71" t="n">
         <v>1125.239834449405</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K71" t="n">
-        <v>9.210000000000001</v>
+        <v>5.71</v>
       </c>
       <c r="L71" t="n">
         <v>2.84</v>
       </c>
       <c r="M71" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="N71" t="n">
-        <v>2.65</v>
+        <v>4.23</v>
       </c>
       <c r="O71" t="n">
         <v>-3.49</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.51</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46181.55208333334</v>
+        <v>46182.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>1161.9</v>
+        <v>1148</v>
       </c>
       <c r="I72" t="n">
         <v>1160.239823203719</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.23</v>
+        <v>-1.43</v>
       </c>
       <c r="L72" t="n">
         <v>3.04</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>6.39</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1042.2</v>
+        <v>1050.7</v>
       </c>
       <c r="I73" t="n">
         <v>1047.914559214262</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K73" t="n">
-        <v>9.220000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="L73" t="n">
         <v>2.04</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>5.99</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46225.55208333334</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>1051.9</v>
+        <v>1044.1</v>
       </c>
       <c r="I74" t="n">
         <v>1044.517323315132</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>0.11</v>
+        <v>-0.63</v>
       </c>
       <c r="L74" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="M74" t="n">
         <v>1.2</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>5.33</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46230.55208333334</v>
+        <v>46231.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>1078.3</v>
+        <v>1107.2</v>
       </c>
       <c r="I75" t="n">
         <v>1089.021872772477</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.28</v>
+        <v>-6.04</v>
       </c>
       <c r="L75" t="n">
-        <v>3.63</v>
+        <v>7.13</v>
       </c>
       <c r="M75" t="n">
         <v>2.5</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>6.04</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46251.38541666666</v>
+        <v>46251.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>1143.8</v>
+        <v>1136.1</v>
       </c>
       <c r="I76" t="n">
         <v>1140.574955317865</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K76" t="n">
-        <v>3.31</v>
+        <v>2.61</v>
       </c>
       <c r="L76" t="n">
         <v>0.92</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>4.55</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46296.38541666666</v>
+        <v>46296.55208333334</v>
       </c>
       <c r="H77" t="n">
-        <v>1002.6</v>
+        <v>1028.9</v>
       </c>
       <c r="I77" t="n">
         <v>1024.402943915042</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>44.83333333333334</v>
+        <v>45</v>
       </c>
       <c r="K77" t="n">
-        <v>11.75</v>
+        <v>9.44</v>
       </c>
       <c r="L77" t="n">
         <v>1.59</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4890,6 +5825,12 @@
       <c r="Q78" t="n">
         <v>33</v>
       </c>
+      <c r="R78" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6992,7 +7933,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="6">
@@ -7002,7 +7943,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -7012,7 +7953,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>97.2</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8">
@@ -7022,7 +7963,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -7032,7 +7973,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.4</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="10">
@@ -7042,7 +7983,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.1</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="11">
@@ -7082,7 +8023,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.35</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="15">
@@ -7092,7 +8033,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.87</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="16">
@@ -7102,7 +8043,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.84</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="17">
@@ -7112,7 +8053,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.23</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="18">
@@ -7122,7 +8063,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.6</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="19">
@@ -7132,7 +8073,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.7</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="20">
@@ -7142,7 +8083,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="21">
@@ -7152,7 +8093,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.17</v>
+        <v>14.48</v>
       </c>
     </row>
     <row r="22">
@@ -7162,7 +8103,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -7172,7 +8113,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -7182,7 +8123,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -7192,7 +8133,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.16</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -7202,7 +8143,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.22</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="27">
@@ -7212,7 +8153,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.7</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="28">
@@ -7222,7 +8163,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
